--- a/csv/model/exogenous prices/formula_exogenous prices_SK.xlsx
+++ b/csv/model/exogenous prices/formula_exogenous prices_SK.xlsx
@@ -1,210 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CIMS\dev\cims-models\csv\model\exogenous prices\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A695268D-75DD-4C28-8EC4-74C925CA0D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF262FB5-3B1E-4D56-9961-A8D06B50453A}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="42">
-  <si>
-    <t>&lt;-- Navigate by typing to search</t>
-  </si>
-  <si>
-    <t>Branch</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Context</t>
-  </si>
-  <si>
-    <t>Sub_Context</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.SK.Electricity</t>
-  </si>
-  <si>
-    <t>SK</t>
-  </si>
-  <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>Service provided</t>
-  </si>
-  <si>
-    <t>GJ</t>
-  </si>
-  <si>
-    <t>Competition type</t>
-  </si>
-  <si>
-    <t>Is supply</t>
-  </si>
-  <si>
-    <t>LCC_financial</t>
-  </si>
-  <si>
-    <t>CER</t>
-  </si>
-  <si>
-    <t>$/GJ</t>
-  </si>
-  <si>
-    <t>Emissions</t>
-  </si>
-  <si>
-    <t>CO2</t>
-  </si>
-  <si>
-    <t>Combustion</t>
-  </si>
-  <si>
-    <t>ECCC, NIR</t>
-  </si>
-  <si>
-    <t>tCO2</t>
-  </si>
-  <si>
-    <t>CH4</t>
-  </si>
-  <si>
-    <t>tCH4</t>
-  </si>
-  <si>
-    <t>N2O</t>
-  </si>
-  <si>
-    <t>tN2O</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.SK.Biodiesel</t>
-  </si>
-  <si>
-    <t>Biodiesel</t>
-  </si>
-  <si>
-    <t>EA Energy Analyses (2015) &amp; Brown et al. (2020)</t>
-  </si>
-  <si>
-    <t>Emissions_biomass</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.SK.Ethanol</t>
-  </si>
-  <si>
-    <t>Ethanol</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.SK.Hydrogen</t>
-  </si>
-  <si>
-    <t>Hydrogen</t>
-  </si>
-  <si>
-    <t>Temporarily use $10.00-3.50/kg</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -223,30 +49,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="Control"/>
       <sheetName val="Macro"/>
@@ -255,6 +137,7 @@
       <sheetName val="Demand"/>
       <sheetName val="Elec markups"/>
       <sheetName val="CER"/>
+      <sheetName val="AFDC"/>
       <sheetName val="Conversions"/>
       <sheetName val="Coefficients"/>
     </sheetNames>
@@ -266,6 +149,14 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
+        <row r="2">
+          <cell r="T2" t="str">
+            <v>Year</v>
+          </cell>
+          <cell r="U2" t="str">
+            <v>Currency</v>
+          </cell>
+        </row>
         <row r="11">
           <cell r="K11">
             <v>758842</v>
@@ -1101,7 +992,393 @@
         </row>
       </sheetData>
       <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5">
+        <row r="11">
+          <cell r="K11">
+            <v>24.680510237764171</v>
+          </cell>
+          <cell r="L11">
+            <v>25.872230739230403</v>
+          </cell>
+          <cell r="M11">
+            <v>26.691279337312114</v>
+          </cell>
+          <cell r="N11">
+            <v>27.034028067375754</v>
+          </cell>
+          <cell r="O11">
+            <v>27.337907595903662</v>
+          </cell>
+          <cell r="P11">
+            <v>27.983685183796911</v>
+          </cell>
+          <cell r="Q11">
+            <v>28.675576915779612</v>
+          </cell>
+          <cell r="R11">
+            <v>29.417269220995323</v>
+          </cell>
+          <cell r="S11">
+            <v>29.965137676021026</v>
+          </cell>
+          <cell r="T11">
+            <v>30.286580006313802</v>
+          </cell>
+          <cell r="U11">
+            <v>30.017551629111804</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>20.058160261081596</v>
+          </cell>
+          <cell r="L12">
+            <v>20.523715667276761</v>
+          </cell>
+          <cell r="M12">
+            <v>20.834470499952019</v>
+          </cell>
+          <cell r="N12">
+            <v>21.162706572015999</v>
+          </cell>
+          <cell r="O12">
+            <v>21.689470223628984</v>
+          </cell>
+          <cell r="P12">
+            <v>22.328044109143288</v>
+          </cell>
+          <cell r="Q12">
+            <v>22.796986513591765</v>
+          </cell>
+          <cell r="R12">
+            <v>23.003396031916907</v>
+          </cell>
+          <cell r="S12">
+            <v>23.00504968758116</v>
+          </cell>
+          <cell r="T12">
+            <v>22.858629438697303</v>
+          </cell>
+          <cell r="U12">
+            <v>22.738540727117996</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>17.029867624028089</v>
+          </cell>
+          <cell r="L13">
+            <v>17.246162874513328</v>
+          </cell>
+          <cell r="M13">
+            <v>17.623009133985107</v>
+          </cell>
+          <cell r="N13">
+            <v>17.917474491621416</v>
+          </cell>
+          <cell r="O13">
+            <v>18.521513956689969</v>
+          </cell>
+          <cell r="P13">
+            <v>19.140477974986471</v>
+          </cell>
+          <cell r="Q13">
+            <v>19.883347256895416</v>
+          </cell>
+          <cell r="R13">
+            <v>20.681271879553687</v>
+          </cell>
+          <cell r="S13">
+            <v>21.548560788410374</v>
+          </cell>
+          <cell r="T13">
+            <v>22.421196419131359</v>
+          </cell>
+          <cell r="U13">
+            <v>23.194837393679148</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>20.183542423256238</v>
+          </cell>
+          <cell r="L14">
+            <v>20.439892909795432</v>
+          </cell>
+          <cell r="M14">
+            <v>20.88652629368875</v>
+          </cell>
+          <cell r="N14">
+            <v>21.235522969372514</v>
+          </cell>
+          <cell r="O14">
+            <v>21.951422186204912</v>
+          </cell>
+          <cell r="P14">
+            <v>22.685009636350809</v>
+          </cell>
+          <cell r="Q14">
+            <v>23.565448018671912</v>
+          </cell>
+          <cell r="R14">
+            <v>24.511136146233184</v>
+          </cell>
+          <cell r="S14">
+            <v>25.53903370146617</v>
+          </cell>
+          <cell r="T14">
+            <v>26.573269639647553</v>
+          </cell>
+          <cell r="U14">
+            <v>27.490177223632511</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>20.183542423256238</v>
+          </cell>
+          <cell r="L15">
+            <v>20.439892909795432</v>
+          </cell>
+          <cell r="M15">
+            <v>20.88652629368875</v>
+          </cell>
+          <cell r="N15">
+            <v>21.235522969372514</v>
+          </cell>
+          <cell r="O15">
+            <v>21.951422186204912</v>
+          </cell>
+          <cell r="P15">
+            <v>22.685009636350809</v>
+          </cell>
+          <cell r="Q15">
+            <v>23.565448018671912</v>
+          </cell>
+          <cell r="R15">
+            <v>24.511136146233184</v>
+          </cell>
+          <cell r="S15">
+            <v>25.53903370146617</v>
+          </cell>
+          <cell r="T15">
+            <v>26.573269639647553</v>
+          </cell>
+          <cell r="U15">
+            <v>27.490177223632511</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>21.255928527363917</v>
+          </cell>
+          <cell r="L16">
+            <v>21.937266625662073</v>
+          </cell>
+          <cell r="M16">
+            <v>22.455700357765892</v>
+          </cell>
+          <cell r="N16">
+            <v>22.902954191124465</v>
+          </cell>
+          <cell r="O16">
+            <v>23.438176499958029</v>
+          </cell>
+          <cell r="P16">
+            <v>24.091181398625451</v>
+          </cell>
+          <cell r="Q16">
+            <v>24.731587821493207</v>
+          </cell>
+          <cell r="R16">
+            <v>25.163285572090135</v>
+          </cell>
+          <cell r="S16">
+            <v>25.472376888620317</v>
+          </cell>
+          <cell r="T16">
+            <v>25.707911658046324</v>
+          </cell>
+          <cell r="U16">
+            <v>25.707042181454018</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17">
+            <v>19.132317490180185</v>
+          </cell>
+          <cell r="L17">
+            <v>19.375316231368064</v>
+          </cell>
+          <cell r="M17">
+            <v>19.7986872404542</v>
+          </cell>
+          <cell r="N17">
+            <v>20.129506810122148</v>
+          </cell>
+          <cell r="O17">
+            <v>20.808119443033267</v>
+          </cell>
+          <cell r="P17">
+            <v>21.503499082562694</v>
+          </cell>
+          <cell r="Q17">
+            <v>22.338081098079744</v>
+          </cell>
+          <cell r="R17">
+            <v>23.234514724006683</v>
+          </cell>
+          <cell r="S17">
+            <v>24.208876063780902</v>
+          </cell>
+          <cell r="T17">
+            <v>25.189245232808826</v>
+          </cell>
+          <cell r="U17">
+            <v>26.058397280314722</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="K20">
+            <v>2004</v>
+          </cell>
+          <cell r="L20">
+            <v>2005</v>
+          </cell>
+          <cell r="M20">
+            <v>2006</v>
+          </cell>
+          <cell r="N20">
+            <v>2007</v>
+          </cell>
+          <cell r="O20">
+            <v>2008</v>
+          </cell>
+          <cell r="P20">
+            <v>2009</v>
+          </cell>
+          <cell r="Q20">
+            <v>2010</v>
+          </cell>
+          <cell r="R20">
+            <v>2011</v>
+          </cell>
+          <cell r="S20">
+            <v>2012</v>
+          </cell>
+          <cell r="T20">
+            <v>2013</v>
+          </cell>
+          <cell r="U20">
+            <v>2014</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="K21">
+            <v>21.218572796755851</v>
+          </cell>
+          <cell r="L21">
+            <v>21.592320910233035</v>
+          </cell>
+          <cell r="M21">
+            <v>22.13773911764077</v>
+          </cell>
+          <cell r="N21">
+            <v>22.758969947220358</v>
+          </cell>
+          <cell r="O21">
+            <v>23.343346696919973</v>
+          </cell>
+          <cell r="P21">
+            <v>24.065393858791815</v>
+          </cell>
+          <cell r="Q21">
+            <v>24.907679682357671</v>
+          </cell>
+          <cell r="R21">
+            <v>25.356983104674974</v>
+          </cell>
+          <cell r="S21">
+            <v>25.826881283710755</v>
+          </cell>
+          <cell r="T21">
+            <v>26.648418938430943</v>
+          </cell>
+          <cell r="U21">
+            <v>27.548569821440612</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>22.804299799664093</v>
+          </cell>
+          <cell r="L22">
+            <v>22.906636756758918</v>
+          </cell>
+          <cell r="M22">
+            <v>23.114932226486012</v>
+          </cell>
+          <cell r="N22">
+            <v>23.424425059716516</v>
+          </cell>
+          <cell r="O22">
+            <v>23.69760617291297</v>
+          </cell>
+          <cell r="P22">
+            <v>24.069741788637899</v>
+          </cell>
+          <cell r="Q22">
+            <v>24.569549116890794</v>
+          </cell>
+          <cell r="R22">
+            <v>24.949766230090052</v>
+          </cell>
+          <cell r="S22">
+            <v>25.37377302832682</v>
+          </cell>
+          <cell r="T22">
+            <v>26.124922653481761</v>
+          </cell>
+          <cell r="U22">
+            <v>26.945557872438641</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>20.92820270530947</v>
+          </cell>
+          <cell r="L23">
+            <v>21.309114277539354</v>
+          </cell>
+          <cell r="M23">
+            <v>21.811915878222962</v>
+          </cell>
+          <cell r="N23">
+            <v>22.36922850642047</v>
+          </cell>
+          <cell r="O23">
+            <v>22.89091673292171</v>
+          </cell>
+          <cell r="P23">
+            <v>23.507252174210983</v>
+          </cell>
+          <cell r="Q23">
+            <v>24.287317864528632</v>
+          </cell>
+          <cell r="R23">
+            <v>24.685217503189087</v>
+          </cell>
+          <cell r="S23">
+            <v>25.122014052215775</v>
+          </cell>
+          <cell r="T23">
+            <v>25.88415968712275</v>
+          </cell>
+          <cell r="U23">
+            <v>26.717473623253522</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="6">
         <row r="2">
           <cell r="K2" t="str">
@@ -1114,9 +1391,136 @@
             <v>Commodity</v>
           </cell>
         </row>
+        <row r="17">
+          <cell r="K17">
+            <v>2022</v>
+          </cell>
+          <cell r="L17" t="str">
+            <v>CAD</v>
+          </cell>
+          <cell r="M17" t="str">
+            <v>GJ</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="K18">
+            <v>2022</v>
+          </cell>
+          <cell r="L18" t="str">
+            <v>CAD</v>
+          </cell>
+          <cell r="M18" t="str">
+            <v>GJ</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="K19">
+            <v>2022</v>
+          </cell>
+          <cell r="L19" t="str">
+            <v>CAD</v>
+          </cell>
+          <cell r="M19" t="str">
+            <v>GJ</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="K20">
+            <v>2022</v>
+          </cell>
+          <cell r="L20" t="str">
+            <v>CAD</v>
+          </cell>
+          <cell r="M20" t="str">
+            <v>GJ</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="K21">
+            <v>2022</v>
+          </cell>
+          <cell r="L21" t="str">
+            <v>CAD</v>
+          </cell>
+          <cell r="M21" t="str">
+            <v>GJ</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>2022</v>
+          </cell>
+          <cell r="L22" t="str">
+            <v>CAD</v>
+          </cell>
+          <cell r="M22" t="str">
+            <v>GJ</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>2022</v>
+          </cell>
+          <cell r="L23" t="str">
+            <v>CAD</v>
+          </cell>
+          <cell r="M23" t="str">
+            <v>GJ</v>
+          </cell>
+        </row>
       </sheetData>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
+      <sheetData sheetId="7">
+        <row r="48">
+          <cell r="R48">
+            <v>18.215701075674659</v>
+          </cell>
+          <cell r="S48">
+            <v>33.871171322160656</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="R49">
+            <v>26.253759143028354</v>
+          </cell>
+          <cell r="S49">
+            <v>33.871171322160656</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="R50">
+            <v>36.040762408001513</v>
+          </cell>
+          <cell r="S50">
+            <v>37.212681638044913</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="R51">
+            <v>33.501604076240795</v>
+          </cell>
+          <cell r="S51">
+            <v>36.669182864691443</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="R52">
+            <v>37.756180411398375</v>
+          </cell>
+          <cell r="S52">
+            <v>42.938526137006974</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="R53">
+            <v>42.010756746555948</v>
+          </cell>
+          <cell r="S53">
+            <v>49.207869409322505</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
         <row r="1">
           <cell r="G1">
             <v>2000</v>
@@ -1300,6 +1704,461 @@
           </cell>
           <cell r="BO1">
             <v>2060</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="K11">
+            <v>3.6</v>
+          </cell>
+          <cell r="L11">
+            <v>3.6</v>
+          </cell>
+          <cell r="M11">
+            <v>3.6</v>
+          </cell>
+          <cell r="N11">
+            <v>3.6</v>
+          </cell>
+          <cell r="O11">
+            <v>3.6</v>
+          </cell>
+          <cell r="P11">
+            <v>3.6</v>
+          </cell>
+          <cell r="Q11">
+            <v>3.6</v>
+          </cell>
+          <cell r="R11">
+            <v>3.6</v>
+          </cell>
+          <cell r="S11">
+            <v>3.6</v>
+          </cell>
+          <cell r="T11">
+            <v>3.6</v>
+          </cell>
+          <cell r="U11">
+            <v>3.6</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>21.275601056803168</v>
+          </cell>
+          <cell r="L12">
+            <v>21.275601056803168</v>
+          </cell>
+          <cell r="M12">
+            <v>21.275601056803168</v>
+          </cell>
+          <cell r="N12">
+            <v>21.275601056803168</v>
+          </cell>
+          <cell r="O12">
+            <v>21.275601056803168</v>
+          </cell>
+          <cell r="P12">
+            <v>21.275601056803168</v>
+          </cell>
+          <cell r="Q12">
+            <v>21.275601056803168</v>
+          </cell>
+          <cell r="R12">
+            <v>21.275601056803168</v>
+          </cell>
+          <cell r="S12">
+            <v>21.275601056803168</v>
+          </cell>
+          <cell r="T12">
+            <v>21.275601056803168</v>
+          </cell>
+          <cell r="U12">
+            <v>21.275601056803168</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>42.500001555910806</v>
+          </cell>
+          <cell r="L13">
+            <v>42.49999462158479</v>
+          </cell>
+          <cell r="M13">
+            <v>42.499993198406727</v>
+          </cell>
+          <cell r="N13">
+            <v>42.500007934339692</v>
+          </cell>
+          <cell r="O13">
+            <v>42.500003902539106</v>
+          </cell>
+          <cell r="P13">
+            <v>42.500005927963386</v>
+          </cell>
+          <cell r="Q13">
+            <v>42.499996053265136</v>
+          </cell>
+          <cell r="R13">
+            <v>42.500008082757489</v>
+          </cell>
+          <cell r="S13">
+            <v>42.500026715920235</v>
+          </cell>
+          <cell r="T13">
+            <v>42.500005546759979</v>
+          </cell>
+          <cell r="U13">
+            <v>42.500005546759979</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>35</v>
+          </cell>
+          <cell r="L14">
+            <v>34.999987755571823</v>
+          </cell>
+          <cell r="M14">
+            <v>35</v>
+          </cell>
+          <cell r="N14">
+            <v>35</v>
+          </cell>
+          <cell r="O14">
+            <v>35.000011988021569</v>
+          </cell>
+          <cell r="P14">
+            <v>34.999976328671664</v>
+          </cell>
+          <cell r="Q14">
+            <v>35.000023044660551</v>
+          </cell>
+          <cell r="R14">
+            <v>35</v>
+          </cell>
+          <cell r="S14">
+            <v>34.999988381090922</v>
+          </cell>
+          <cell r="T14">
+            <v>34.999988640675021</v>
+          </cell>
+          <cell r="U14">
+            <v>34.999977954144619</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>120</v>
+          </cell>
+          <cell r="L15">
+            <v>120</v>
+          </cell>
+          <cell r="M15">
+            <v>120</v>
+          </cell>
+          <cell r="N15">
+            <v>120</v>
+          </cell>
+          <cell r="O15">
+            <v>120</v>
+          </cell>
+          <cell r="P15">
+            <v>120</v>
+          </cell>
+          <cell r="Q15">
+            <v>120</v>
+          </cell>
+          <cell r="R15">
+            <v>120</v>
+          </cell>
+          <cell r="S15">
+            <v>120</v>
+          </cell>
+          <cell r="T15">
+            <v>120</v>
+          </cell>
+          <cell r="U15">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>37.399981406303262</v>
+          </cell>
+          <cell r="L16">
+            <v>37.400184612679666</v>
+          </cell>
+          <cell r="M16">
+            <v>37.400059355987537</v>
+          </cell>
+          <cell r="N16">
+            <v>37.400157760962927</v>
+          </cell>
+          <cell r="O16">
+            <v>37.40004043482994</v>
+          </cell>
+          <cell r="P16">
+            <v>37.400068271036012</v>
+          </cell>
+          <cell r="Q16">
+            <v>37.400177462289264</v>
+          </cell>
+          <cell r="R16">
+            <v>37.400238829734306</v>
+          </cell>
+          <cell r="S16">
+            <v>37.39993851829081</v>
+          </cell>
+          <cell r="T16">
+            <v>37.400161140754925</v>
+          </cell>
+          <cell r="U16">
+            <v>37.400081034931844</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17">
+            <v>26.799897075220859</v>
+          </cell>
+          <cell r="L17">
+            <v>26.799897075220859</v>
+          </cell>
+          <cell r="M17">
+            <v>26.799897075220859</v>
+          </cell>
+          <cell r="N17">
+            <v>26.799897075220859</v>
+          </cell>
+          <cell r="O17">
+            <v>26.799897075220859</v>
+          </cell>
+          <cell r="P17">
+            <v>26.799897075220859</v>
+          </cell>
+          <cell r="Q17">
+            <v>26.799897075220859</v>
+          </cell>
+          <cell r="R17">
+            <v>26.799897075220859</v>
+          </cell>
+          <cell r="S17">
+            <v>26.799897075220859</v>
+          </cell>
+          <cell r="T17">
+            <v>26.799897075220859</v>
+          </cell>
+          <cell r="U17">
+            <v>26.799897075220859</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="K18">
+            <v>38.21000005608883</v>
+          </cell>
+          <cell r="L18">
+            <v>38.259998958056819</v>
+          </cell>
+          <cell r="M18">
+            <v>38.260000180720937</v>
+          </cell>
+          <cell r="N18">
+            <v>38.110000608339433</v>
+          </cell>
+          <cell r="O18">
+            <v>38.409998944225379</v>
+          </cell>
+          <cell r="P18">
+            <v>38.430000915151403</v>
+          </cell>
+          <cell r="Q18">
+            <v>38.51999993949601</v>
+          </cell>
+          <cell r="R18">
+            <v>38.560001088530569</v>
+          </cell>
+          <cell r="S18">
+            <v>38.740000970806214</v>
+          </cell>
+          <cell r="T18">
+            <v>38.85000097656868</v>
+          </cell>
+          <cell r="U18">
+            <v>38.999999222988272</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="K19">
+            <v>38.647544562117609</v>
+          </cell>
+          <cell r="L19">
+            <v>38.647544328371573</v>
+          </cell>
+          <cell r="M19">
+            <v>38.647538364410046</v>
+          </cell>
+          <cell r="N19">
+            <v>38.647532379989407</v>
+          </cell>
+          <cell r="O19">
+            <v>38.647536489743565</v>
+          </cell>
+          <cell r="P19">
+            <v>38.647537590620246</v>
+          </cell>
+          <cell r="Q19">
+            <v>38.647532447156081</v>
+          </cell>
+          <cell r="R19">
+            <v>38.647541819225708</v>
+          </cell>
+          <cell r="S19">
+            <v>38.647535763672678</v>
+          </cell>
+          <cell r="T19">
+            <v>38.647553606699262</v>
+          </cell>
+          <cell r="U19">
+            <v>38.649998943212829</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="K20">
+            <v>25.309999732126116</v>
+          </cell>
+          <cell r="L20">
+            <v>25.310004648873331</v>
+          </cell>
+          <cell r="M20">
+            <v>25.310008937742619</v>
+          </cell>
+          <cell r="N20">
+            <v>25.309965026132161</v>
+          </cell>
+          <cell r="O20">
+            <v>25.310016100068115</v>
+          </cell>
+          <cell r="P20">
+            <v>25.30995543220482</v>
+          </cell>
+          <cell r="Q20">
+            <v>25.309980203756457</v>
+          </cell>
+          <cell r="R20">
+            <v>25.310013677607543</v>
+          </cell>
+          <cell r="S20">
+            <v>25.309978730946472</v>
+          </cell>
+          <cell r="T20">
+            <v>25.309978730946472</v>
+          </cell>
+          <cell r="U20">
+            <v>25.309978730946472</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="K21">
+            <v>36.08</v>
+          </cell>
+          <cell r="L21">
+            <v>36.08</v>
+          </cell>
+          <cell r="M21">
+            <v>36.08</v>
+          </cell>
+          <cell r="N21">
+            <v>36.08</v>
+          </cell>
+          <cell r="O21">
+            <v>36.08</v>
+          </cell>
+          <cell r="P21">
+            <v>36.08</v>
+          </cell>
+          <cell r="Q21">
+            <v>36.08</v>
+          </cell>
+          <cell r="R21">
+            <v>36.08</v>
+          </cell>
+          <cell r="S21">
+            <v>36.08</v>
+          </cell>
+          <cell r="T21">
+            <v>36.08</v>
+          </cell>
+          <cell r="U21">
+            <v>36.08</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>18</v>
+          </cell>
+          <cell r="L22">
+            <v>18.000000170755115</v>
+          </cell>
+          <cell r="M22">
+            <v>18.000000343487216</v>
+          </cell>
+          <cell r="N22">
+            <v>17.999999715692439</v>
+          </cell>
+          <cell r="O22">
+            <v>17.999999523496939</v>
+          </cell>
+          <cell r="P22">
+            <v>17.999999577905282</v>
+          </cell>
+          <cell r="Q22">
+            <v>17.999999701146166</v>
+          </cell>
+          <cell r="R22">
+            <v>17.999999899867035</v>
+          </cell>
+          <cell r="S22">
+            <v>18.000000620051409</v>
+          </cell>
+          <cell r="T22">
+            <v>18.000000410619947</v>
+          </cell>
+          <cell r="U22">
+            <v>17.999999697412118</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="K23">
+            <v>704.54700000000003</v>
+          </cell>
+          <cell r="L23">
+            <v>704.54700000000003</v>
+          </cell>
+          <cell r="M23">
+            <v>704.54700000000003</v>
+          </cell>
+          <cell r="N23">
+            <v>704.54700000000003</v>
+          </cell>
+          <cell r="O23">
+            <v>704.54700000000003</v>
+          </cell>
+          <cell r="P23">
+            <v>704.54700000000003</v>
+          </cell>
+          <cell r="Q23">
+            <v>704.54700000000003</v>
+          </cell>
+          <cell r="R23">
+            <v>704.54700000000003</v>
+          </cell>
+          <cell r="S23">
+            <v>704.54700000000003</v>
+          </cell>
+          <cell r="T23">
+            <v>704.54700000000003</v>
+          </cell>
+          <cell r="U23">
+            <v>704.54700000000003</v>
           </cell>
         </row>
         <row r="29">
@@ -12904,1519 +13763,2016 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C68A40E-00AB-4AC5-9A94-8B845B18B1C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>&lt;-- Navigate by typing to search</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sub_Context</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>2000</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>2005</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>2010</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>2015</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>2020</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>2025</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>2030</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>2035</v>
       </c>
-      <c r="U2">
+      <c r="U2" t="n">
         <v>2040</v>
       </c>
-      <c r="V2">
+      <c r="V2" t="n">
         <v>2045</v>
       </c>
-      <c r="W2">
+      <c r="W2" t="n">
         <v>2050</v>
       </c>
-      <c r="X2" t="s">
-        <v>13</v>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" t="s">
-        <v>18</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Electricity</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Service provided</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>4</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Electricity</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Competition type</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Electricity</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Is supply</t>
+        </is>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" cm="1">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Electricity</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LCC_financial</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>CER</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>$/GJ</t>
+        </is>
+      </c>
+      <c r="M6">
         <f t="array" ref="M6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(M$2,[1]!CER_year))</f>
-        <v>18.87119975589912</v>
-      </c>
-      <c r="N6" cm="1">
+        <v/>
+      </c>
+      <c r="N6">
         <f t="array" ref="N6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(N$2,[1]!CER_year))</f>
-        <v>20.054571632219091</v>
-      </c>
-      <c r="O6" cm="1">
+        <v/>
+      </c>
+      <c r="O6">
         <f t="array" ref="O6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(O$2,[1]!CER_year))</f>
-        <v>22.479254311443441</v>
-      </c>
-      <c r="P6" cm="1">
+        <v/>
+      </c>
+      <c r="P6">
         <f t="array" ref="P6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(P$2,[1]!CER_year))</f>
-        <v>25.421474866158949</v>
-      </c>
-      <c r="Q6" cm="1">
+        <v/>
+      </c>
+      <c r="Q6">
         <f t="array" ref="Q6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(Q$2,[1]!CER_year))</f>
-        <v>29.418058936757351</v>
-      </c>
-      <c r="R6" cm="1">
+        <v/>
+      </c>
+      <c r="R6">
         <f t="array" ref="R6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(R$2,[1]!CER_year))</f>
-        <v>30.972746062531844</v>
-      </c>
-      <c r="S6" cm="1">
+        <v/>
+      </c>
+      <c r="S6">
         <f t="array" ref="S6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(S$2,[1]!CER_year))</f>
-        <v>31.797943331654654</v>
-      </c>
-      <c r="T6" cm="1">
+        <v/>
+      </c>
+      <c r="T6">
         <f t="array" ref="T6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(T$2,[1]!CER_year))</f>
-        <v>32.066931792689836</v>
-      </c>
-      <c r="U6" cm="1">
+        <v/>
+      </c>
+      <c r="U6">
         <f t="array" ref="U6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(U$2,[1]!CER_year))</f>
-        <v>33.257248040134968</v>
-      </c>
-      <c r="V6" cm="1">
+        <v/>
+      </c>
+      <c r="V6">
         <f t="array" ref="V6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(V$2,[1]!CER_year))</f>
-        <v>35.121156385650117</v>
-      </c>
-      <c r="W6" cm="1">
+        <v/>
+      </c>
+      <c r="W6">
         <f t="array" ref="W6">INDEX([1]!CER_prod_cost,_xlfn.XMATCH($C6&amp;"Production cost"&amp;$A6,[1]!CER_prod_cost_index),_xlfn.XMATCH(W$2,[1]!CER_year))</f>
-        <v>35.965926458636005</v>
+        <v/>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Electricity</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>tCO2</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="U7">
+      <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="V7">
+      <c r="V7" t="n">
         <v>0</v>
       </c>
-      <c r="W7">
+      <c r="W7" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Electricity</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>tCH4</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>0</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>0</v>
       </c>
-      <c r="U8">
+      <c r="U8" t="n">
         <v>0</v>
       </c>
-      <c r="V8">
+      <c r="V8" t="n">
         <v>0</v>
       </c>
-      <c r="W8">
+      <c r="W8" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>N2O</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>tN2O</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>0</v>
       </c>
-      <c r="U9">
+      <c r="U9" t="n">
         <v>0</v>
       </c>
-      <c r="V9">
+      <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="W9">
+      <c r="W9" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Biodiesel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Biodiesel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Service provided</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" t="s">
-        <v>4</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Biodiesel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Biodiesel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Competition type</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" t="s">
-        <v>20</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Biodiesel</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Biodiesel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Is supply</t>
+        </is>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" t="s">
-        <v>23</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Biodiesel</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Biodiesel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LCC_financial</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>AFDC 2023</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>$/GJ</t>
+        </is>
       </c>
       <c r="M13">
-        <v>35.188099999999999</v>
+        <f t="array" ref="M13:R13">TRANSPOSE([1]AFDC!$S$48:$S$53)</f>
+        <v/>
       </c>
       <c r="N13">
-        <v>35.188099999999999</v>
+        <f/>
+        <v/>
       </c>
       <c r="O13">
-        <v>35.188099999999999</v>
+        <f/>
+        <v/>
       </c>
       <c r="P13">
-        <v>35.188099999999999</v>
+        <f/>
+        <v/>
       </c>
       <c r="Q13">
-        <v>35.188099999999999</v>
+        <f/>
+        <v/>
       </c>
       <c r="R13">
-        <v>35.188099999999999</v>
+        <f/>
+        <v/>
       </c>
       <c r="S13">
-        <v>35.188099999999999</v>
+        <f>R13</f>
+        <v/>
       </c>
       <c r="T13">
-        <v>35.188099999999999</v>
+        <f>S13</f>
+        <v/>
       </c>
       <c r="U13">
-        <v>35.188099999999999</v>
+        <f>T13</f>
+        <v/>
       </c>
       <c r="V13">
-        <v>35.188099999999999</v>
+        <f>U13</f>
+        <v/>
       </c>
       <c r="W13">
-        <v>35.188099999999999</v>
+        <f>V13</f>
+        <v/>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M14" cm="1">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Biodiesel</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Biodiesel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Emissions_biomass</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>tCO2</t>
+        </is>
+      </c>
+      <c r="M14">
         <f t="array" ref="M14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(M$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(M$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
-      </c>
-      <c r="N14" cm="1">
+        <v/>
+      </c>
+      <c r="N14">
         <f t="array" ref="N14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(N$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(N$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
-      </c>
-      <c r="O14" cm="1">
+        <v/>
+      </c>
+      <c r="O14">
         <f t="array" ref="O14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(O$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(O$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
-      </c>
-      <c r="P14" cm="1">
+        <v/>
+      </c>
+      <c r="P14">
         <f t="array" ref="P14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(P$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(P$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
-      </c>
-      <c r="Q14" cm="1">
+        <v/>
+      </c>
+      <c r="Q14">
         <f t="array" ref="Q14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(Q$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(Q$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
-      </c>
-      <c r="R14" cm="1">
+        <v/>
+      </c>
+      <c r="R14">
         <f t="array" ref="R14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(R$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(R$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
-      </c>
-      <c r="S14" cm="1">
+        <v/>
+      </c>
+      <c r="S14">
         <f t="array" ref="S14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(S$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(S$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
-      </c>
-      <c r="T14" cm="1">
+        <v/>
+      </c>
+      <c r="T14">
         <f t="array" ref="T14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(T$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(T$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
-      </c>
-      <c r="U14" cm="1">
+        <v/>
+      </c>
+      <c r="U14">
         <f t="array" ref="U14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(U$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(U$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
-      </c>
-      <c r="V14" cm="1">
+        <v/>
+      </c>
+      <c r="V14">
         <f t="array" ref="V14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(V$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(V$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
-      </c>
-      <c r="W14" cm="1">
+        <v/>
+      </c>
+      <c r="W14">
         <f t="array" ref="W14">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E14,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(W$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E14,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(W$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.4244372161799493E-2</v>
+        <v/>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" t="s">
-        <v>28</v>
-      </c>
-      <c r="M15" cm="1">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Biodiesel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Biodiesel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>tCO2</t>
+        </is>
+      </c>
+      <c r="M15">
         <f t="array" ref="M15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(M$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="N15" cm="1">
+        <v/>
+      </c>
+      <c r="N15">
         <f t="array" ref="N15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(N$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="O15" cm="1">
+        <v/>
+      </c>
+      <c r="O15">
         <f t="array" ref="O15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(O$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="P15" cm="1">
+        <v/>
+      </c>
+      <c r="P15">
         <f t="array" ref="P15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(P$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" cm="1">
+        <v/>
+      </c>
+      <c r="Q15">
         <f t="array" ref="Q15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(Q$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="R15" cm="1">
+        <v/>
+      </c>
+      <c r="R15">
         <f t="array" ref="R15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(R$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="S15" cm="1">
+        <v/>
+      </c>
+      <c r="S15">
         <f t="array" ref="S15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(S$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="T15" cm="1">
+        <v/>
+      </c>
+      <c r="T15">
         <f t="array" ref="T15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(T$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="U15" cm="1">
+        <v/>
+      </c>
+      <c r="U15">
         <f t="array" ref="U15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(U$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="V15" cm="1">
+        <v/>
+      </c>
+      <c r="V15">
         <f t="array" ref="V15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(V$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="W15" cm="1">
+        <v/>
+      </c>
+      <c r="W15">
         <f t="array" ref="W15">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E15,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(W$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" cm="1">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Biodiesel</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Biodiesel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>tCH4</t>
+        </is>
+      </c>
+      <c r="M16">
         <f t="array" ref="M16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(M$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="N16" cm="1">
+        <v/>
+      </c>
+      <c r="N16">
         <f t="array" ref="N16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(N$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="O16" cm="1">
+        <v/>
+      </c>
+      <c r="O16">
         <f t="array" ref="O16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(O$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="P16" cm="1">
+        <v/>
+      </c>
+      <c r="P16">
         <f t="array" ref="P16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(P$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" cm="1">
+        <v/>
+      </c>
+      <c r="Q16">
         <f t="array" ref="Q16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(Q$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="R16" cm="1">
+        <v/>
+      </c>
+      <c r="R16">
         <f t="array" ref="R16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(R$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="S16" cm="1">
+        <v/>
+      </c>
+      <c r="S16">
         <f t="array" ref="S16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(S$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="T16" cm="1">
+        <v/>
+      </c>
+      <c r="T16">
         <f t="array" ref="T16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(T$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="U16" cm="1">
+        <v/>
+      </c>
+      <c r="U16">
         <f t="array" ref="U16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(U$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="V16" cm="1">
+        <v/>
+      </c>
+      <c r="V16">
         <f t="array" ref="V16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(V$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="W16" cm="1">
+        <v/>
+      </c>
+      <c r="W16">
         <f t="array" ref="W16">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E16,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(W$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17" cm="1">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Biodiesel</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Biodiesel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>N2O</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>tN2O</t>
+        </is>
+      </c>
+      <c r="M17">
         <f t="array" ref="M17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(M$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="N17" cm="1">
+        <v/>
+      </c>
+      <c r="N17">
         <f t="array" ref="N17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(N$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="O17" cm="1">
+        <v/>
+      </c>
+      <c r="O17">
         <f t="array" ref="O17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(O$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="P17" cm="1">
+        <v/>
+      </c>
+      <c r="P17">
         <f t="array" ref="P17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(P$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" cm="1">
+        <v/>
+      </c>
+      <c r="Q17">
         <f t="array" ref="Q17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(Q$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="R17" cm="1">
+        <v/>
+      </c>
+      <c r="R17">
         <f t="array" ref="R17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(R$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="S17" cm="1">
+        <v/>
+      </c>
+      <c r="S17">
         <f t="array" ref="S17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(S$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="T17" cm="1">
+        <v/>
+      </c>
+      <c r="T17">
         <f t="array" ref="T17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(T$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="U17" cm="1">
+        <v/>
+      </c>
+      <c r="U17">
         <f t="array" ref="U17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(U$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="V17" cm="1">
+        <v/>
+      </c>
+      <c r="V17">
         <f t="array" ref="V17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(V$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="W17" cm="1">
+        <v/>
+      </c>
+      <c r="W17">
         <f t="array" ref="W17">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E17,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(W$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" t="s">
-        <v>18</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Ethanol</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ethanol</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Service provided</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" t="s">
-        <v>4</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Ethanol</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ethanol</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Competition type</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" t="s">
-        <v>20</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Ethanol</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ethanol</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Is supply</t>
+        </is>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" t="s">
-        <v>23</v>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Ethanol</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ethanol</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LCC_financial</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>AFDC 2023</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>$/GJ</t>
+        </is>
       </c>
       <c r="M21">
-        <v>33</v>
+        <f t="array" ref="M21:R21">TRANSPOSE([1]AFDC!$R$48:$R$53)</f>
+        <v/>
       </c>
       <c r="N21">
-        <v>33</v>
+        <f/>
+        <v/>
       </c>
       <c r="O21">
-        <v>33</v>
+        <f/>
+        <v/>
       </c>
       <c r="P21">
-        <v>33</v>
+        <f/>
+        <v/>
       </c>
       <c r="Q21">
-        <v>33</v>
+        <f/>
+        <v/>
       </c>
       <c r="R21">
-        <v>33</v>
+        <f/>
+        <v/>
       </c>
       <c r="S21">
-        <v>33</v>
+        <f>R21</f>
+        <v/>
       </c>
       <c r="T21">
-        <v>33</v>
+        <f>S21</f>
+        <v/>
       </c>
       <c r="U21">
-        <v>33</v>
+        <f>T21</f>
+        <v/>
       </c>
       <c r="V21">
-        <v>33</v>
+        <f>U21</f>
+        <v/>
       </c>
       <c r="W21">
-        <v>33</v>
+        <f>V21</f>
+        <v/>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" t="s">
-        <v>25</v>
-      </c>
-      <c r="I22" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" t="s">
-        <v>28</v>
-      </c>
-      <c r="M22" cm="1">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Ethanol</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ethanol</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Emissions_biomass</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>tCO2</t>
+        </is>
+      </c>
+      <c r="M22">
         <f t="array" ref="M22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(M$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(M$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
-      </c>
-      <c r="N22" cm="1">
+        <v/>
+      </c>
+      <c r="N22">
         <f t="array" ref="N22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(N$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(N$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
-      </c>
-      <c r="O22" cm="1">
+        <v/>
+      </c>
+      <c r="O22">
         <f t="array" ref="O22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(O$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(O$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
-      </c>
-      <c r="P22" cm="1">
+        <v/>
+      </c>
+      <c r="P22">
         <f t="array" ref="P22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(P$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(P$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
-      </c>
-      <c r="Q22" cm="1">
+        <v/>
+      </c>
+      <c r="Q22">
         <f t="array" ref="Q22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(Q$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(Q$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
-      </c>
-      <c r="R22" cm="1">
+        <v/>
+      </c>
+      <c r="R22">
         <f t="array" ref="R22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(R$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(R$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
-      </c>
-      <c r="S22" cm="1">
+        <v/>
+      </c>
+      <c r="S22">
         <f t="array" ref="S22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(S$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(S$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
-      </c>
-      <c r="T22" cm="1">
+        <v/>
+      </c>
+      <c r="T22">
         <f t="array" ref="T22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(T$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(T$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
-      </c>
-      <c r="U22" cm="1">
+        <v/>
+      </c>
+      <c r="U22">
         <f t="array" ref="U22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(U$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(U$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
-      </c>
-      <c r="V22" cm="1">
+        <v/>
+      </c>
+      <c r="V22">
         <f t="array" ref="V22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(V$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(V$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
-      </c>
-      <c r="W22" cm="1">
+        <v/>
+      </c>
+      <c r="W22">
         <f t="array" ref="W22">INDEX([1]Coefficients!$G$60:$BO$79,_xlfn.XMATCH($E22,[1]Coefficients!$B$60:$B$79),_xlfn.XMATCH(W$2,[1]Coefficients!$G$1:$BO$1))/INDEX([1]Coefficients!$G$29:$BO$48,_xlfn.XMATCH($E22,[1]Coefficients!$B$29:$B$48),_xlfn.XMATCH(W$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>7.0926315828688483E-2</v>
+        <v/>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" t="s">
-        <v>25</v>
-      </c>
-      <c r="I23" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" t="s">
-        <v>27</v>
-      </c>
-      <c r="L23" t="s">
-        <v>28</v>
-      </c>
-      <c r="M23" cm="1">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Ethanol</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ethanol</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>tCO2</t>
+        </is>
+      </c>
+      <c r="M23">
         <f t="array" ref="M23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(M$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="N23" cm="1">
+        <v/>
+      </c>
+      <c r="N23">
         <f t="array" ref="N23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(N$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="O23" cm="1">
+        <v/>
+      </c>
+      <c r="O23">
         <f t="array" ref="O23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(O$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="P23" cm="1">
+        <v/>
+      </c>
+      <c r="P23">
         <f t="array" ref="P23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(P$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="Q23" cm="1">
+        <v/>
+      </c>
+      <c r="Q23">
         <f t="array" ref="Q23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(Q$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="R23" cm="1">
+        <v/>
+      </c>
+      <c r="R23">
         <f t="array" ref="R23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(R$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="S23" cm="1">
+        <v/>
+      </c>
+      <c r="S23">
         <f t="array" ref="S23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(S$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="T23" cm="1">
+        <v/>
+      </c>
+      <c r="T23">
         <f t="array" ref="T23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(T$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="U23" cm="1">
+        <v/>
+      </c>
+      <c r="U23">
         <f t="array" ref="U23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(U$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="V23" cm="1">
+        <v/>
+      </c>
+      <c r="V23">
         <f t="array" ref="V23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(V$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="W23" cm="1">
+        <v/>
+      </c>
+      <c r="W23">
         <f t="array" ref="W23">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E23,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(W$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" t="s">
-        <v>29</v>
-      </c>
-      <c r="I24" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" t="s">
-        <v>30</v>
-      </c>
-      <c r="M24" cm="1">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Ethanol</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ethanol</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>tCH4</t>
+        </is>
+      </c>
+      <c r="M24">
         <f t="array" ref="M24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(M$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="N24" cm="1">
+        <v/>
+      </c>
+      <c r="N24">
         <f t="array" ref="N24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(N$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="O24" cm="1">
+        <v/>
+      </c>
+      <c r="O24">
         <f t="array" ref="O24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(O$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="P24" cm="1">
+        <v/>
+      </c>
+      <c r="P24">
         <f t="array" ref="P24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(P$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" cm="1">
+        <v/>
+      </c>
+      <c r="Q24">
         <f t="array" ref="Q24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(Q$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="R24" cm="1">
+        <v/>
+      </c>
+      <c r="R24">
         <f t="array" ref="R24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(R$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="S24" cm="1">
+        <v/>
+      </c>
+      <c r="S24">
         <f t="array" ref="S24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(S$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="T24" cm="1">
+        <v/>
+      </c>
+      <c r="T24">
         <f t="array" ref="T24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(T$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="U24" cm="1">
+        <v/>
+      </c>
+      <c r="U24">
         <f t="array" ref="U24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(U$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="V24" cm="1">
+        <v/>
+      </c>
+      <c r="V24">
         <f t="array" ref="V24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(V$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="W24" cm="1">
+        <v/>
+      </c>
+      <c r="W24">
         <f t="array" ref="W24">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E24,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(W$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" t="s">
-        <v>27</v>
-      </c>
-      <c r="L25" t="s">
-        <v>32</v>
-      </c>
-      <c r="M25" cm="1">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Ethanol</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ethanol</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>N2O</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>tN2O</t>
+        </is>
+      </c>
+      <c r="M25">
         <f t="array" ref="M25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(M$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="N25" cm="1">
+        <v/>
+      </c>
+      <c r="N25">
         <f t="array" ref="N25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(N$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="O25" cm="1">
+        <v/>
+      </c>
+      <c r="O25">
         <f t="array" ref="O25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(O$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="P25" cm="1">
+        <v/>
+      </c>
+      <c r="P25">
         <f t="array" ref="P25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(P$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" cm="1">
+        <v/>
+      </c>
+      <c r="Q25">
         <f t="array" ref="Q25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(Q$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="R25" cm="1">
+        <v/>
+      </c>
+      <c r="R25">
         <f t="array" ref="R25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(R$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="S25" cm="1">
+        <v/>
+      </c>
+      <c r="S25">
         <f t="array" ref="S25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(S$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="T25" cm="1">
+        <v/>
+      </c>
+      <c r="T25">
         <f t="array" ref="T25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(T$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="U25" cm="1">
+        <v/>
+      </c>
+      <c r="U25">
         <f t="array" ref="U25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(U$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="V25" cm="1">
+        <v/>
+      </c>
+      <c r="V25">
         <f t="array" ref="V25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(V$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
-      </c>
-      <c r="W25" cm="1">
+        <v/>
+      </c>
+      <c r="W25">
         <f t="array" ref="W25">INDEX([1]Coefficients!$G$132:$BO$151,_xlfn.XMATCH($E25,[1]Coefficients!$B$132:$B$151),_xlfn.XMATCH(W$2,[1]Coefficients!$G$1:$BO$1))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" t="s">
-        <v>40</v>
-      </c>
-      <c r="G26" t="s">
-        <v>17</v>
-      </c>
-      <c r="L26" t="s">
-        <v>18</v>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Hydrogen</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Service provided</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>GJ</t>
+        </is>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" t="s">
-        <v>40</v>
-      </c>
-      <c r="G27" t="s">
-        <v>19</v>
-      </c>
-      <c r="H27" t="s">
-        <v>4</v>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Hydrogen</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Competition type</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" t="s">
-        <v>40</v>
-      </c>
-      <c r="G28" t="s">
-        <v>20</v>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Hydrogen</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Is supply</t>
+        </is>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L29" t="s">
-        <v>23</v>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Hydrogen</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>LCC_financial</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>$/GJ</t>
+        </is>
       </c>
       <c r="M29">
         <f>10/0.142</f>
-        <v>70.422535211267615</v>
+        <v/>
       </c>
       <c r="N29">
-        <f t="shared" ref="N29:W29" si="0">M29*0.9</f>
-        <v>63.380281690140855</v>
+        <f>M29*0.9</f>
+        <v/>
       </c>
       <c r="O29">
-        <f t="shared" si="0"/>
-        <v>57.042253521126767</v>
+        <f>N29*0.9</f>
+        <v/>
       </c>
       <c r="P29">
-        <f t="shared" si="0"/>
-        <v>51.338028169014095</v>
+        <f>O29*0.9</f>
+        <v/>
       </c>
       <c r="Q29">
-        <f t="shared" si="0"/>
-        <v>46.204225352112687</v>
+        <f>P29*0.9</f>
+        <v/>
       </c>
       <c r="R29">
-        <f t="shared" si="0"/>
-        <v>41.583802816901418</v>
+        <f>Q29*0.9</f>
+        <v/>
       </c>
       <c r="S29">
-        <f t="shared" si="0"/>
-        <v>37.425422535211275</v>
+        <f>R29*0.9</f>
+        <v/>
       </c>
       <c r="T29">
-        <f t="shared" si="0"/>
-        <v>33.682880281690146</v>
+        <f>S29*0.9</f>
+        <v/>
       </c>
       <c r="U29">
-        <f t="shared" si="0"/>
-        <v>30.314592253521131</v>
+        <f>T29*0.9</f>
+        <v/>
       </c>
       <c r="V29">
-        <f t="shared" si="0"/>
-        <v>27.283133028169019</v>
+        <f>U29*0.9</f>
+        <v/>
       </c>
       <c r="W29">
-        <f t="shared" si="0"/>
-        <v>24.554819725352118</v>
-      </c>
-      <c r="X29" t="s">
-        <v>41</v>
+        <f>V29*0.9</f>
+        <v/>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Temporarily use $10.00-3.50/kg</t>
+        </is>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" t="s">
-        <v>40</v>
-      </c>
-      <c r="G30" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" t="s">
-        <v>25</v>
-      </c>
-      <c r="I30" t="s">
-        <v>26</v>
-      </c>
-      <c r="K30" t="s">
-        <v>27</v>
-      </c>
-      <c r="L30" t="s">
-        <v>28</v>
-      </c>
-      <c r="M30">
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Hydrogen</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>tCO2</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30">
+      <c r="N30" t="n">
         <v>0</v>
       </c>
-      <c r="O30">
+      <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" t="n">
         <v>0</v>
       </c>
-      <c r="R30">
+      <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>0</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>0</v>
       </c>
-      <c r="U30">
+      <c r="U30" t="n">
         <v>0</v>
       </c>
-      <c r="V30">
+      <c r="V30" t="n">
         <v>0</v>
       </c>
-      <c r="W30">
+      <c r="W30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" t="s">
-        <v>40</v>
-      </c>
-      <c r="G31" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" t="s">
-        <v>29</v>
-      </c>
-      <c r="I31" t="s">
-        <v>26</v>
-      </c>
-      <c r="K31" t="s">
-        <v>27</v>
-      </c>
-      <c r="L31" t="s">
-        <v>30</v>
-      </c>
-      <c r="M31">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Hydrogen</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>tCH4</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31">
+      <c r="N31" t="n">
         <v>0</v>
       </c>
-      <c r="O31">
+      <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" t="n">
         <v>0</v>
       </c>
-      <c r="R31">
+      <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31">
+      <c r="S31" t="n">
         <v>0</v>
       </c>
-      <c r="T31">
+      <c r="T31" t="n">
         <v>0</v>
       </c>
-      <c r="U31">
+      <c r="U31" t="n">
         <v>0</v>
       </c>
-      <c r="V31">
+      <c r="V31" t="n">
         <v>0</v>
       </c>
-      <c r="W31">
+      <c r="W31" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" t="s">
-        <v>40</v>
-      </c>
-      <c r="G32" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" t="s">
-        <v>26</v>
-      </c>
-      <c r="K32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" t="s">
-        <v>32</v>
-      </c>
-      <c r="M32">
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.SK.Hydrogen</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Emissions</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>N2O</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ECCC, NIR</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>tN2O</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32">
+      <c r="N32" t="n">
         <v>0</v>
       </c>
-      <c r="O32">
+      <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" t="n">
         <v>0</v>
       </c>
-      <c r="R32">
+      <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>0</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>0</v>
       </c>
-      <c r="U32">
+      <c r="U32" t="n">
         <v>0</v>
       </c>
-      <c r="V32">
+      <c r="V32" t="n">
         <v>0</v>
       </c>
-      <c r="W32">
+      <c r="W32" t="n">
         <v>0</v>
       </c>
     </row>

--- a/csv/model/exogenous prices/formula_exogenous prices_SK.xlsx
+++ b/csv/model/exogenous prices/formula_exogenous prices_SK.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -140,6 +140,7 @@
       <sheetName val="AFDC"/>
       <sheetName val="Conversions"/>
       <sheetName val="Coefficients"/>
+      <sheetName val="macro inputs"/>
     </sheetNames>
     <definedNames>
       <definedName name="CER_prod_cost" refersTo="='Prices'!$K$11:$U$23"/>
@@ -997,386 +998,6 @@
           <cell r="K11">
             <v>24.680510237764171</v>
           </cell>
-          <cell r="L11">
-            <v>25.872230739230403</v>
-          </cell>
-          <cell r="M11">
-            <v>26.691279337312114</v>
-          </cell>
-          <cell r="N11">
-            <v>27.034028067375754</v>
-          </cell>
-          <cell r="O11">
-            <v>27.337907595903662</v>
-          </cell>
-          <cell r="P11">
-            <v>27.983685183796911</v>
-          </cell>
-          <cell r="Q11">
-            <v>28.675576915779612</v>
-          </cell>
-          <cell r="R11">
-            <v>29.417269220995323</v>
-          </cell>
-          <cell r="S11">
-            <v>29.965137676021026</v>
-          </cell>
-          <cell r="T11">
-            <v>30.286580006313802</v>
-          </cell>
-          <cell r="U11">
-            <v>30.017551629111804</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="K12">
-            <v>20.058160261081596</v>
-          </cell>
-          <cell r="L12">
-            <v>20.523715667276761</v>
-          </cell>
-          <cell r="M12">
-            <v>20.834470499952019</v>
-          </cell>
-          <cell r="N12">
-            <v>21.162706572015999</v>
-          </cell>
-          <cell r="O12">
-            <v>21.689470223628984</v>
-          </cell>
-          <cell r="P12">
-            <v>22.328044109143288</v>
-          </cell>
-          <cell r="Q12">
-            <v>22.796986513591765</v>
-          </cell>
-          <cell r="R12">
-            <v>23.003396031916907</v>
-          </cell>
-          <cell r="S12">
-            <v>23.00504968758116</v>
-          </cell>
-          <cell r="T12">
-            <v>22.858629438697303</v>
-          </cell>
-          <cell r="U12">
-            <v>22.738540727117996</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="K13">
-            <v>17.029867624028089</v>
-          </cell>
-          <cell r="L13">
-            <v>17.246162874513328</v>
-          </cell>
-          <cell r="M13">
-            <v>17.623009133985107</v>
-          </cell>
-          <cell r="N13">
-            <v>17.917474491621416</v>
-          </cell>
-          <cell r="O13">
-            <v>18.521513956689969</v>
-          </cell>
-          <cell r="P13">
-            <v>19.140477974986471</v>
-          </cell>
-          <cell r="Q13">
-            <v>19.883347256895416</v>
-          </cell>
-          <cell r="R13">
-            <v>20.681271879553687</v>
-          </cell>
-          <cell r="S13">
-            <v>21.548560788410374</v>
-          </cell>
-          <cell r="T13">
-            <v>22.421196419131359</v>
-          </cell>
-          <cell r="U13">
-            <v>23.194837393679148</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="K14">
-            <v>20.183542423256238</v>
-          </cell>
-          <cell r="L14">
-            <v>20.439892909795432</v>
-          </cell>
-          <cell r="M14">
-            <v>20.88652629368875</v>
-          </cell>
-          <cell r="N14">
-            <v>21.235522969372514</v>
-          </cell>
-          <cell r="O14">
-            <v>21.951422186204912</v>
-          </cell>
-          <cell r="P14">
-            <v>22.685009636350809</v>
-          </cell>
-          <cell r="Q14">
-            <v>23.565448018671912</v>
-          </cell>
-          <cell r="R14">
-            <v>24.511136146233184</v>
-          </cell>
-          <cell r="S14">
-            <v>25.53903370146617</v>
-          </cell>
-          <cell r="T14">
-            <v>26.573269639647553</v>
-          </cell>
-          <cell r="U14">
-            <v>27.490177223632511</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="K15">
-            <v>20.183542423256238</v>
-          </cell>
-          <cell r="L15">
-            <v>20.439892909795432</v>
-          </cell>
-          <cell r="M15">
-            <v>20.88652629368875</v>
-          </cell>
-          <cell r="N15">
-            <v>21.235522969372514</v>
-          </cell>
-          <cell r="O15">
-            <v>21.951422186204912</v>
-          </cell>
-          <cell r="P15">
-            <v>22.685009636350809</v>
-          </cell>
-          <cell r="Q15">
-            <v>23.565448018671912</v>
-          </cell>
-          <cell r="R15">
-            <v>24.511136146233184</v>
-          </cell>
-          <cell r="S15">
-            <v>25.53903370146617</v>
-          </cell>
-          <cell r="T15">
-            <v>26.573269639647553</v>
-          </cell>
-          <cell r="U15">
-            <v>27.490177223632511</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="K16">
-            <v>21.255928527363917</v>
-          </cell>
-          <cell r="L16">
-            <v>21.937266625662073</v>
-          </cell>
-          <cell r="M16">
-            <v>22.455700357765892</v>
-          </cell>
-          <cell r="N16">
-            <v>22.902954191124465</v>
-          </cell>
-          <cell r="O16">
-            <v>23.438176499958029</v>
-          </cell>
-          <cell r="P16">
-            <v>24.091181398625451</v>
-          </cell>
-          <cell r="Q16">
-            <v>24.731587821493207</v>
-          </cell>
-          <cell r="R16">
-            <v>25.163285572090135</v>
-          </cell>
-          <cell r="S16">
-            <v>25.472376888620317</v>
-          </cell>
-          <cell r="T16">
-            <v>25.707911658046324</v>
-          </cell>
-          <cell r="U16">
-            <v>25.707042181454018</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="K17">
-            <v>19.132317490180185</v>
-          </cell>
-          <cell r="L17">
-            <v>19.375316231368064</v>
-          </cell>
-          <cell r="M17">
-            <v>19.7986872404542</v>
-          </cell>
-          <cell r="N17">
-            <v>20.129506810122148</v>
-          </cell>
-          <cell r="O17">
-            <v>20.808119443033267</v>
-          </cell>
-          <cell r="P17">
-            <v>21.503499082562694</v>
-          </cell>
-          <cell r="Q17">
-            <v>22.338081098079744</v>
-          </cell>
-          <cell r="R17">
-            <v>23.234514724006683</v>
-          </cell>
-          <cell r="S17">
-            <v>24.208876063780902</v>
-          </cell>
-          <cell r="T17">
-            <v>25.189245232808826</v>
-          </cell>
-          <cell r="U17">
-            <v>26.058397280314722</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="K20">
-            <v>2004</v>
-          </cell>
-          <cell r="L20">
-            <v>2005</v>
-          </cell>
-          <cell r="M20">
-            <v>2006</v>
-          </cell>
-          <cell r="N20">
-            <v>2007</v>
-          </cell>
-          <cell r="O20">
-            <v>2008</v>
-          </cell>
-          <cell r="P20">
-            <v>2009</v>
-          </cell>
-          <cell r="Q20">
-            <v>2010</v>
-          </cell>
-          <cell r="R20">
-            <v>2011</v>
-          </cell>
-          <cell r="S20">
-            <v>2012</v>
-          </cell>
-          <cell r="T20">
-            <v>2013</v>
-          </cell>
-          <cell r="U20">
-            <v>2014</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="K21">
-            <v>21.218572796755851</v>
-          </cell>
-          <cell r="L21">
-            <v>21.592320910233035</v>
-          </cell>
-          <cell r="M21">
-            <v>22.13773911764077</v>
-          </cell>
-          <cell r="N21">
-            <v>22.758969947220358</v>
-          </cell>
-          <cell r="O21">
-            <v>23.343346696919973</v>
-          </cell>
-          <cell r="P21">
-            <v>24.065393858791815</v>
-          </cell>
-          <cell r="Q21">
-            <v>24.907679682357671</v>
-          </cell>
-          <cell r="R21">
-            <v>25.356983104674974</v>
-          </cell>
-          <cell r="S21">
-            <v>25.826881283710755</v>
-          </cell>
-          <cell r="T21">
-            <v>26.648418938430943</v>
-          </cell>
-          <cell r="U21">
-            <v>27.548569821440612</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="K22">
-            <v>22.804299799664093</v>
-          </cell>
-          <cell r="L22">
-            <v>22.906636756758918</v>
-          </cell>
-          <cell r="M22">
-            <v>23.114932226486012</v>
-          </cell>
-          <cell r="N22">
-            <v>23.424425059716516</v>
-          </cell>
-          <cell r="O22">
-            <v>23.69760617291297</v>
-          </cell>
-          <cell r="P22">
-            <v>24.069741788637899</v>
-          </cell>
-          <cell r="Q22">
-            <v>24.569549116890794</v>
-          </cell>
-          <cell r="R22">
-            <v>24.949766230090052</v>
-          </cell>
-          <cell r="S22">
-            <v>25.37377302832682</v>
-          </cell>
-          <cell r="T22">
-            <v>26.124922653481761</v>
-          </cell>
-          <cell r="U22">
-            <v>26.945557872438641</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="K23">
-            <v>20.92820270530947</v>
-          </cell>
-          <cell r="L23">
-            <v>21.309114277539354</v>
-          </cell>
-          <cell r="M23">
-            <v>21.811915878222962</v>
-          </cell>
-          <cell r="N23">
-            <v>22.36922850642047</v>
-          </cell>
-          <cell r="O23">
-            <v>22.89091673292171</v>
-          </cell>
-          <cell r="P23">
-            <v>23.507252174210983</v>
-          </cell>
-          <cell r="Q23">
-            <v>24.287317864528632</v>
-          </cell>
-          <cell r="R23">
-            <v>24.685217503189087</v>
-          </cell>
-          <cell r="S23">
-            <v>25.122014052215775</v>
-          </cell>
-          <cell r="T23">
-            <v>25.88415968712275</v>
-          </cell>
-          <cell r="U23">
-            <v>26.717473623253522</v>
-          </cell>
         </row>
       </sheetData>
       <sheetData sheetId="6">
@@ -1389,83 +1010,6 @@
           </cell>
           <cell r="M2" t="str">
             <v>Commodity</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="K17">
-            <v>2022</v>
-          </cell>
-          <cell r="L17" t="str">
-            <v>CAD</v>
-          </cell>
-          <cell r="M17" t="str">
-            <v>GJ</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="K18">
-            <v>2022</v>
-          </cell>
-          <cell r="L18" t="str">
-            <v>CAD</v>
-          </cell>
-          <cell r="M18" t="str">
-            <v>GJ</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="K19">
-            <v>2022</v>
-          </cell>
-          <cell r="L19" t="str">
-            <v>CAD</v>
-          </cell>
-          <cell r="M19" t="str">
-            <v>GJ</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="K20">
-            <v>2022</v>
-          </cell>
-          <cell r="L20" t="str">
-            <v>CAD</v>
-          </cell>
-          <cell r="M20" t="str">
-            <v>GJ</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="K21">
-            <v>2022</v>
-          </cell>
-          <cell r="L21" t="str">
-            <v>CAD</v>
-          </cell>
-          <cell r="M21" t="str">
-            <v>GJ</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="K22">
-            <v>2022</v>
-          </cell>
-          <cell r="L22" t="str">
-            <v>CAD</v>
-          </cell>
-          <cell r="M22" t="str">
-            <v>GJ</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="K23">
-            <v>2022</v>
-          </cell>
-          <cell r="L23" t="str">
-            <v>CAD</v>
-          </cell>
-          <cell r="M23" t="str">
-            <v>GJ</v>
           </cell>
         </row>
       </sheetData>
@@ -1706,461 +1250,6 @@
             <v>2060</v>
           </cell>
         </row>
-        <row r="11">
-          <cell r="K11">
-            <v>3.6</v>
-          </cell>
-          <cell r="L11">
-            <v>3.6</v>
-          </cell>
-          <cell r="M11">
-            <v>3.6</v>
-          </cell>
-          <cell r="N11">
-            <v>3.6</v>
-          </cell>
-          <cell r="O11">
-            <v>3.6</v>
-          </cell>
-          <cell r="P11">
-            <v>3.6</v>
-          </cell>
-          <cell r="Q11">
-            <v>3.6</v>
-          </cell>
-          <cell r="R11">
-            <v>3.6</v>
-          </cell>
-          <cell r="S11">
-            <v>3.6</v>
-          </cell>
-          <cell r="T11">
-            <v>3.6</v>
-          </cell>
-          <cell r="U11">
-            <v>3.6</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="K12">
-            <v>21.275601056803168</v>
-          </cell>
-          <cell r="L12">
-            <v>21.275601056803168</v>
-          </cell>
-          <cell r="M12">
-            <v>21.275601056803168</v>
-          </cell>
-          <cell r="N12">
-            <v>21.275601056803168</v>
-          </cell>
-          <cell r="O12">
-            <v>21.275601056803168</v>
-          </cell>
-          <cell r="P12">
-            <v>21.275601056803168</v>
-          </cell>
-          <cell r="Q12">
-            <v>21.275601056803168</v>
-          </cell>
-          <cell r="R12">
-            <v>21.275601056803168</v>
-          </cell>
-          <cell r="S12">
-            <v>21.275601056803168</v>
-          </cell>
-          <cell r="T12">
-            <v>21.275601056803168</v>
-          </cell>
-          <cell r="U12">
-            <v>21.275601056803168</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="K13">
-            <v>42.500001555910806</v>
-          </cell>
-          <cell r="L13">
-            <v>42.49999462158479</v>
-          </cell>
-          <cell r="M13">
-            <v>42.499993198406727</v>
-          </cell>
-          <cell r="N13">
-            <v>42.500007934339692</v>
-          </cell>
-          <cell r="O13">
-            <v>42.500003902539106</v>
-          </cell>
-          <cell r="P13">
-            <v>42.500005927963386</v>
-          </cell>
-          <cell r="Q13">
-            <v>42.499996053265136</v>
-          </cell>
-          <cell r="R13">
-            <v>42.500008082757489</v>
-          </cell>
-          <cell r="S13">
-            <v>42.500026715920235</v>
-          </cell>
-          <cell r="T13">
-            <v>42.500005546759979</v>
-          </cell>
-          <cell r="U13">
-            <v>42.500005546759979</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="K14">
-            <v>35</v>
-          </cell>
-          <cell r="L14">
-            <v>34.999987755571823</v>
-          </cell>
-          <cell r="M14">
-            <v>35</v>
-          </cell>
-          <cell r="N14">
-            <v>35</v>
-          </cell>
-          <cell r="O14">
-            <v>35.000011988021569</v>
-          </cell>
-          <cell r="P14">
-            <v>34.999976328671664</v>
-          </cell>
-          <cell r="Q14">
-            <v>35.000023044660551</v>
-          </cell>
-          <cell r="R14">
-            <v>35</v>
-          </cell>
-          <cell r="S14">
-            <v>34.999988381090922</v>
-          </cell>
-          <cell r="T14">
-            <v>34.999988640675021</v>
-          </cell>
-          <cell r="U14">
-            <v>34.999977954144619</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="K15">
-            <v>120</v>
-          </cell>
-          <cell r="L15">
-            <v>120</v>
-          </cell>
-          <cell r="M15">
-            <v>120</v>
-          </cell>
-          <cell r="N15">
-            <v>120</v>
-          </cell>
-          <cell r="O15">
-            <v>120</v>
-          </cell>
-          <cell r="P15">
-            <v>120</v>
-          </cell>
-          <cell r="Q15">
-            <v>120</v>
-          </cell>
-          <cell r="R15">
-            <v>120</v>
-          </cell>
-          <cell r="S15">
-            <v>120</v>
-          </cell>
-          <cell r="T15">
-            <v>120</v>
-          </cell>
-          <cell r="U15">
-            <v>120</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="K16">
-            <v>37.399981406303262</v>
-          </cell>
-          <cell r="L16">
-            <v>37.400184612679666</v>
-          </cell>
-          <cell r="M16">
-            <v>37.400059355987537</v>
-          </cell>
-          <cell r="N16">
-            <v>37.400157760962927</v>
-          </cell>
-          <cell r="O16">
-            <v>37.40004043482994</v>
-          </cell>
-          <cell r="P16">
-            <v>37.400068271036012</v>
-          </cell>
-          <cell r="Q16">
-            <v>37.400177462289264</v>
-          </cell>
-          <cell r="R16">
-            <v>37.400238829734306</v>
-          </cell>
-          <cell r="S16">
-            <v>37.39993851829081</v>
-          </cell>
-          <cell r="T16">
-            <v>37.400161140754925</v>
-          </cell>
-          <cell r="U16">
-            <v>37.400081034931844</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="K17">
-            <v>26.799897075220859</v>
-          </cell>
-          <cell r="L17">
-            <v>26.799897075220859</v>
-          </cell>
-          <cell r="M17">
-            <v>26.799897075220859</v>
-          </cell>
-          <cell r="N17">
-            <v>26.799897075220859</v>
-          </cell>
-          <cell r="O17">
-            <v>26.799897075220859</v>
-          </cell>
-          <cell r="P17">
-            <v>26.799897075220859</v>
-          </cell>
-          <cell r="Q17">
-            <v>26.799897075220859</v>
-          </cell>
-          <cell r="R17">
-            <v>26.799897075220859</v>
-          </cell>
-          <cell r="S17">
-            <v>26.799897075220859</v>
-          </cell>
-          <cell r="T17">
-            <v>26.799897075220859</v>
-          </cell>
-          <cell r="U17">
-            <v>26.799897075220859</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="K18">
-            <v>38.21000005608883</v>
-          </cell>
-          <cell r="L18">
-            <v>38.259998958056819</v>
-          </cell>
-          <cell r="M18">
-            <v>38.260000180720937</v>
-          </cell>
-          <cell r="N18">
-            <v>38.110000608339433</v>
-          </cell>
-          <cell r="O18">
-            <v>38.409998944225379</v>
-          </cell>
-          <cell r="P18">
-            <v>38.430000915151403</v>
-          </cell>
-          <cell r="Q18">
-            <v>38.51999993949601</v>
-          </cell>
-          <cell r="R18">
-            <v>38.560001088530569</v>
-          </cell>
-          <cell r="S18">
-            <v>38.740000970806214</v>
-          </cell>
-          <cell r="T18">
-            <v>38.85000097656868</v>
-          </cell>
-          <cell r="U18">
-            <v>38.999999222988272</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="K19">
-            <v>38.647544562117609</v>
-          </cell>
-          <cell r="L19">
-            <v>38.647544328371573</v>
-          </cell>
-          <cell r="M19">
-            <v>38.647538364410046</v>
-          </cell>
-          <cell r="N19">
-            <v>38.647532379989407</v>
-          </cell>
-          <cell r="O19">
-            <v>38.647536489743565</v>
-          </cell>
-          <cell r="P19">
-            <v>38.647537590620246</v>
-          </cell>
-          <cell r="Q19">
-            <v>38.647532447156081</v>
-          </cell>
-          <cell r="R19">
-            <v>38.647541819225708</v>
-          </cell>
-          <cell r="S19">
-            <v>38.647535763672678</v>
-          </cell>
-          <cell r="T19">
-            <v>38.647553606699262</v>
-          </cell>
-          <cell r="U19">
-            <v>38.649998943212829</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="K20">
-            <v>25.309999732126116</v>
-          </cell>
-          <cell r="L20">
-            <v>25.310004648873331</v>
-          </cell>
-          <cell r="M20">
-            <v>25.310008937742619</v>
-          </cell>
-          <cell r="N20">
-            <v>25.309965026132161</v>
-          </cell>
-          <cell r="O20">
-            <v>25.310016100068115</v>
-          </cell>
-          <cell r="P20">
-            <v>25.30995543220482</v>
-          </cell>
-          <cell r="Q20">
-            <v>25.309980203756457</v>
-          </cell>
-          <cell r="R20">
-            <v>25.310013677607543</v>
-          </cell>
-          <cell r="S20">
-            <v>25.309978730946472</v>
-          </cell>
-          <cell r="T20">
-            <v>25.309978730946472</v>
-          </cell>
-          <cell r="U20">
-            <v>25.309978730946472</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="K21">
-            <v>36.08</v>
-          </cell>
-          <cell r="L21">
-            <v>36.08</v>
-          </cell>
-          <cell r="M21">
-            <v>36.08</v>
-          </cell>
-          <cell r="N21">
-            <v>36.08</v>
-          </cell>
-          <cell r="O21">
-            <v>36.08</v>
-          </cell>
-          <cell r="P21">
-            <v>36.08</v>
-          </cell>
-          <cell r="Q21">
-            <v>36.08</v>
-          </cell>
-          <cell r="R21">
-            <v>36.08</v>
-          </cell>
-          <cell r="S21">
-            <v>36.08</v>
-          </cell>
-          <cell r="T21">
-            <v>36.08</v>
-          </cell>
-          <cell r="U21">
-            <v>36.08</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="K22">
-            <v>18</v>
-          </cell>
-          <cell r="L22">
-            <v>18.000000170755115</v>
-          </cell>
-          <cell r="M22">
-            <v>18.000000343487216</v>
-          </cell>
-          <cell r="N22">
-            <v>17.999999715692439</v>
-          </cell>
-          <cell r="O22">
-            <v>17.999999523496939</v>
-          </cell>
-          <cell r="P22">
-            <v>17.999999577905282</v>
-          </cell>
-          <cell r="Q22">
-            <v>17.999999701146166</v>
-          </cell>
-          <cell r="R22">
-            <v>17.999999899867035</v>
-          </cell>
-          <cell r="S22">
-            <v>18.000000620051409</v>
-          </cell>
-          <cell r="T22">
-            <v>18.000000410619947</v>
-          </cell>
-          <cell r="U22">
-            <v>17.999999697412118</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="K23">
-            <v>704.54700000000003</v>
-          </cell>
-          <cell r="L23">
-            <v>704.54700000000003</v>
-          </cell>
-          <cell r="M23">
-            <v>704.54700000000003</v>
-          </cell>
-          <cell r="N23">
-            <v>704.54700000000003</v>
-          </cell>
-          <cell r="O23">
-            <v>704.54700000000003</v>
-          </cell>
-          <cell r="P23">
-            <v>704.54700000000003</v>
-          </cell>
-          <cell r="Q23">
-            <v>704.54700000000003</v>
-          </cell>
-          <cell r="R23">
-            <v>704.54700000000003</v>
-          </cell>
-          <cell r="S23">
-            <v>704.54700000000003</v>
-          </cell>
-          <cell r="T23">
-            <v>704.54700000000003</v>
-          </cell>
-          <cell r="U23">
-            <v>704.54700000000003</v>
-          </cell>
-        </row>
         <row r="29">
           <cell r="B29" t="str">
             <v>Biodiesel</v>
@@ -13442,6 +12531,7 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="10" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -13764,12 +12854,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -13901,7 +12991,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -13933,7 +13023,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -13965,7 +13055,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -13995,7 +13085,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -14076,7 +13166,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -14156,7 +13246,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -14236,7 +13326,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -14316,7 +13406,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -14348,7 +13438,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -14380,7 +13470,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -14410,7 +13500,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14427,25 +13517,20 @@
         <f t="array" ref="M13:R13">TRANSPOSE([1]AFDC!$S$48:$S$53)</f>
         <v/>
       </c>
-      <c r="N13">
-        <f/>
-        <v/>
-      </c>
-      <c r="O13">
-        <f/>
-        <v/>
-      </c>
-      <c r="P13">
-        <f/>
-        <v/>
-      </c>
-      <c r="Q13">
-        <f/>
-        <v/>
-      </c>
-      <c r="R13">
-        <f/>
-        <v/>
+      <c r="N13" t="n">
+        <v>33.87117132216066</v>
+      </c>
+      <c r="O13" t="n">
+        <v>37.21268163804491</v>
+      </c>
+      <c r="P13" t="n">
+        <v>36.66918286469144</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>42.93852613700697</v>
+      </c>
+      <c r="R13" t="n">
+        <v>49.20786940932251</v>
       </c>
       <c r="S13">
         <f>R13</f>
@@ -14491,7 +13576,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emissions_biomass</t>
+          <t>emissions_biomass</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -14577,7 +13662,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -14668,7 +13753,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -14759,7 +13844,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -14850,7 +13935,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -14882,7 +13967,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -14914,7 +13999,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -14944,7 +14029,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -14961,25 +14046,20 @@
         <f t="array" ref="M21:R21">TRANSPOSE([1]AFDC!$R$48:$R$53)</f>
         <v/>
       </c>
-      <c r="N21">
-        <f/>
-        <v/>
-      </c>
-      <c r="O21">
-        <f/>
-        <v/>
-      </c>
-      <c r="P21">
-        <f/>
-        <v/>
-      </c>
-      <c r="Q21">
-        <f/>
-        <v/>
-      </c>
-      <c r="R21">
-        <f/>
-        <v/>
+      <c r="N21" t="n">
+        <v>26.25375914302835</v>
+      </c>
+      <c r="O21" t="n">
+        <v>36.04076240800151</v>
+      </c>
+      <c r="P21" t="n">
+        <v>33.5016040762408</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>37.75618041139838</v>
+      </c>
+      <c r="R21" t="n">
+        <v>42.01075674655595</v>
       </c>
       <c r="S21">
         <f>R21</f>
@@ -15025,7 +14105,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Emissions_biomass</t>
+          <t>emissions_biomass</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -15111,7 +14191,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -15202,7 +14282,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -15293,7 +14373,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -15384,7 +14464,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Service provided</t>
+          <t>service_provide</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -15416,7 +14496,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Competition type</t>
+          <t>competition</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -15448,7 +14528,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Is supply</t>
+          <t>is_supply</t>
         </is>
       </c>
       <c r="H28" t="b">
@@ -15478,7 +14558,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LCC_financial</t>
+          <t>lcc_financial</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -15559,7 +14639,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -15639,7 +14719,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -15719,7 +14799,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>emissions</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
